--- a/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_papillary_renal_cell_carcinoma_combined.xlsx
+++ b/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_papillary_renal_cell_carcinoma_combined.xlsx
@@ -518,13 +518,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.86</v>
+        <v>0.19</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>4144</v>
+        <v>120852</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>46</v>
